--- a/artfynd/A 17520-2026 artfynd.xlsx
+++ b/artfynd/A 17520-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128796466</v>
+        <v>128689087</v>
       </c>
       <c r="B2" t="n">
-        <v>90376</v>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6292</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulgrön kantmusseron</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma viridilutescens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -709,17 +709,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fiskarudden, Norrskog Svartsjö, Upl</t>
+          <t>Fiskarudden, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655400</v>
+        <v>655365</v>
       </c>
       <c r="R2" t="n">
-        <v>6584714</v>
+        <v>6584795</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,6 +782,337 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126524846</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92510</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1143</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blekticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Haploporus tuberculosus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Fiskarudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>655406</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6584845</v>
+      </c>
+      <c r="S3" t="n">
+        <v>11</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sånga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>David Morger</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>David Morger</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126524844</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91867</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fiskarudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>655406</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6584845</v>
+      </c>
+      <c r="S4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sånga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Morger</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>David Morger</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128796466</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90721</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6292</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulgrön kantmusseron</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tricholoma viridilutescens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fiskarudden, Norrskog Svartsjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>655400</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6584714</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sånga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Morger</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>David Morger</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17520-2026 artfynd.xlsx
+++ b/artfynd/A 17520-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1136,6 +1136,127 @@
       <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128796466</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135402172</v>
+      </c>
+      <c r="B6" t="n">
+        <v>9605</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>101479</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Läderbagge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Osmoderma eremita</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fiskarudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>655403</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6584841</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sånga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>David Morger</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>David Morger</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402172</t>
         </is>
       </c>
     </row>
@@ -1145,6 +1266,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17520-2026 artfynd.xlsx
+++ b/artfynd/A 17520-2026 artfynd.xlsx
@@ -1144,7 +1144,7 @@
         <v>135402172</v>
       </c>
       <c r="B6" t="n">
-        <v>9605</v>
+        <v>9607</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
